--- a/wi_pop_countylevel_hisp.xlsx
+++ b/wi_pop_countylevel_hisp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mckelvey/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8C8403-D134-104C-9D3B-92E72CAE5432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19F0DAE-02A0-D44B-8440-DF33FF34AB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17780" yWindow="1140" windowWidth="27640" windowHeight="16620" xr2:uid="{5B6A6753-0C8F-BF44-9344-50151CB1B676}"/>
+    <workbookView xWindow="17780" yWindow="1140" windowWidth="27640" windowHeight="16620" activeTab="1" xr2:uid="{5B6A6753-0C8F-BF44-9344-50151CB1B676}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-Hispanic" sheetId="1" r:id="rId1"/>
@@ -1711,195 +1711,195 @@
         <v>73</v>
       </c>
       <c r="B4" s="2">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C4" s="2">
         <v>2021</v>
       </c>
       <c r="D4" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>902</v>
-      </c>
-      <c r="C5">
-        <v>825</v>
-      </c>
-      <c r="D5">
-        <v>804</v>
+        <v>41</v>
+      </c>
+      <c r="B5" s="1">
+        <v>153567</v>
+      </c>
+      <c r="C5" s="1">
+        <v>154328</v>
+      </c>
+      <c r="D5" s="1">
+        <v>156915</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>473</v>
-      </c>
-      <c r="C6">
-        <v>435</v>
-      </c>
-      <c r="D6">
-        <v>403</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>42251</v>
+      </c>
+      <c r="C6" s="1">
+        <v>42765</v>
+      </c>
+      <c r="D6" s="1">
+        <v>44366</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1">
-        <v>1520</v>
+        <v>28182</v>
       </c>
       <c r="C7" s="1">
-        <v>1406</v>
+        <v>28766</v>
       </c>
       <c r="D7" s="1">
-        <v>1295</v>
+        <v>29716</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>294</v>
-      </c>
-      <c r="C8">
-        <v>292</v>
-      </c>
-      <c r="D8">
-        <v>272</v>
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26386</v>
+      </c>
+      <c r="C8" s="1">
+        <v>27015</v>
+      </c>
+      <c r="D8" s="1">
+        <v>28005</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>28005</v>
+        <v>24709</v>
       </c>
       <c r="C9" s="1">
-        <v>27015</v>
+        <v>25037</v>
       </c>
       <c r="D9" s="1">
-        <v>26386</v>
+        <v>25629</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>388</v>
-      </c>
-      <c r="C10">
-        <v>335</v>
-      </c>
-      <c r="D10">
-        <v>318</v>
+        <v>68</v>
+      </c>
+      <c r="B10" s="1">
+        <v>21971</v>
+      </c>
+      <c r="C10" s="1">
+        <v>22536</v>
+      </c>
+      <c r="D10" s="1">
+        <v>23569</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>309</v>
-      </c>
-      <c r="C11">
-        <v>284</v>
-      </c>
-      <c r="D11">
-        <v>276</v>
+        <v>54</v>
+      </c>
+      <c r="B11" s="1">
+        <v>15826</v>
+      </c>
+      <c r="C11" s="1">
+        <v>16148</v>
+      </c>
+      <c r="D11" s="1">
+        <v>16461</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1">
-        <v>3004</v>
+        <v>12385</v>
       </c>
       <c r="C12" s="1">
-        <v>2892</v>
+        <v>12469</v>
       </c>
       <c r="D12" s="1">
-        <v>2828</v>
+        <v>12809</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1">
-        <v>1335</v>
+        <v>9514</v>
       </c>
       <c r="C13" s="1">
-        <v>1261</v>
+        <v>9899</v>
       </c>
       <c r="D13" s="1">
-        <v>1260</v>
+        <v>10205</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1">
-        <v>2299</v>
+        <v>8737</v>
       </c>
       <c r="C14" s="1">
-        <v>2182</v>
+        <v>8859</v>
       </c>
       <c r="D14" s="1">
-        <v>2125</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1">
-        <v>2332</v>
+        <v>8411</v>
       </c>
       <c r="C15" s="1">
-        <v>2226</v>
+        <v>8587</v>
       </c>
       <c r="D15" s="1">
-        <v>2127</v>
+        <v>8774</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16">
-        <v>285</v>
-      </c>
-      <c r="C16">
-        <v>289</v>
-      </c>
-      <c r="D16">
-        <v>252</v>
+        <v>28</v>
+      </c>
+      <c r="B16" s="1">
+        <v>7252</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7328</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7471</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B17" s="1">
-        <v>44366</v>
+        <v>6780</v>
       </c>
       <c r="C17" s="1">
-        <v>42765</v>
+        <v>7002</v>
       </c>
       <c r="D17" s="1">
-        <v>42251</v>
+        <v>7285</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1907,727 +1907,727 @@
         <v>13</v>
       </c>
       <c r="B18" s="1">
-        <v>6065</v>
+        <v>5503</v>
       </c>
       <c r="C18" s="1">
         <v>5708</v>
       </c>
       <c r="D18" s="1">
-        <v>5503</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1">
-        <v>1267</v>
+        <v>4826</v>
       </c>
       <c r="C19" s="1">
-        <v>1214</v>
+        <v>5027</v>
       </c>
       <c r="D19" s="1">
-        <v>1151</v>
+        <v>5247</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <v>869</v>
-      </c>
-      <c r="C20">
-        <v>789</v>
-      </c>
-      <c r="D20">
-        <v>791</v>
+        <v>37</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4467</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4623</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4911</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1">
-        <v>1172</v>
+        <v>4097</v>
       </c>
       <c r="C21" s="1">
-        <v>1096</v>
+        <v>4202</v>
       </c>
       <c r="D21" s="1">
-        <v>1069</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1">
-        <v>3527</v>
+        <v>4096</v>
       </c>
       <c r="C22" s="1">
-        <v>3397</v>
+        <v>4130</v>
       </c>
       <c r="D22" s="1">
-        <v>3279</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23">
-        <v>101</v>
-      </c>
-      <c r="C23">
-        <v>86</v>
-      </c>
-      <c r="D23">
-        <v>80</v>
+        <v>62</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3994</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3996</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3981</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1">
-        <v>7285</v>
+        <v>3279</v>
       </c>
       <c r="C24" s="1">
-        <v>7002</v>
+        <v>3397</v>
       </c>
       <c r="D24" s="1">
-        <v>6780</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25">
-        <v>186</v>
-      </c>
-      <c r="C25">
-        <v>170</v>
-      </c>
-      <c r="D25">
-        <v>143</v>
+        <v>46</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3105</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3254</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3460</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1">
-        <v>1338</v>
+        <v>3049</v>
       </c>
       <c r="C26" s="1">
-        <v>1272</v>
+        <v>3099</v>
       </c>
       <c r="D26" s="1">
-        <v>1278</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1">
-        <v>1600</v>
+        <v>2828</v>
       </c>
       <c r="C27" s="1">
-        <v>1517</v>
+        <v>2892</v>
       </c>
       <c r="D27" s="1">
-        <v>1487</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1">
-        <v>1072</v>
+        <v>2699</v>
       </c>
       <c r="C28" s="1">
-        <v>1030</v>
-      </c>
-      <c r="D28">
-        <v>995</v>
+        <v>2835</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2920</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29">
-        <v>518</v>
-      </c>
-      <c r="C29">
-        <v>502</v>
-      </c>
-      <c r="D29">
-        <v>450</v>
+        <v>50</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2656</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2745</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2969</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30">
-        <v>79</v>
-      </c>
-      <c r="C30">
-        <v>70</v>
-      </c>
-      <c r="D30">
-        <v>63</v>
+        <v>42</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2575</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2674</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2715</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31">
-        <v>751</v>
-      </c>
-      <c r="C31">
-        <v>698</v>
-      </c>
-      <c r="D31">
-        <v>650</v>
+        <v>72</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2430</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2581</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2760</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B32" s="1">
-        <v>7471</v>
+        <v>2127</v>
       </c>
       <c r="C32" s="1">
-        <v>7328</v>
+        <v>2226</v>
       </c>
       <c r="D32" s="1">
-        <v>7252</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33">
-        <v>776</v>
-      </c>
-      <c r="C33">
-        <v>780</v>
-      </c>
-      <c r="D33">
-        <v>740</v>
+        <v>9</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2125</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2182</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2299</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1">
-        <v>25629</v>
+        <v>1865</v>
       </c>
       <c r="C34" s="1">
-        <v>25037</v>
+        <v>1917</v>
       </c>
       <c r="D34" s="1">
-        <v>24709</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35">
-        <v>909</v>
-      </c>
-      <c r="C35">
-        <v>828</v>
-      </c>
-      <c r="D35">
-        <v>838</v>
+        <v>70</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1688</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1719</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1786</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B36" s="1">
-        <v>3308</v>
+        <v>1487</v>
       </c>
       <c r="C36" s="1">
-        <v>3099</v>
+        <v>1517</v>
       </c>
       <c r="D36" s="1">
-        <v>3049</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B37" s="1">
-        <v>1165</v>
+        <v>1295</v>
       </c>
       <c r="C37" s="1">
-        <v>1075</v>
+        <v>1406</v>
       </c>
       <c r="D37" s="1">
-        <v>1057</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38">
-        <v>469</v>
-      </c>
-      <c r="C38">
-        <v>443</v>
-      </c>
-      <c r="D38">
-        <v>457</v>
+        <v>22</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1278</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1272</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1338</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39">
-        <v>575</v>
-      </c>
-      <c r="C39">
-        <v>552</v>
-      </c>
-      <c r="D39">
-        <v>513</v>
+        <v>8</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1260</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1261</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1335</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
-        <v>4585</v>
+        <v>1232</v>
       </c>
       <c r="C40" s="1">
-        <v>4202</v>
+        <v>1190</v>
       </c>
       <c r="D40" s="1">
-        <v>4097</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1">
-        <v>4911</v>
+        <v>1186</v>
       </c>
       <c r="C41" s="1">
-        <v>4623</v>
+        <v>1259</v>
       </c>
       <c r="D41" s="1">
-        <v>4467</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B42" s="1">
-        <v>1230</v>
+        <v>1151</v>
       </c>
       <c r="C42" s="1">
-        <v>1143</v>
+        <v>1214</v>
       </c>
       <c r="D42" s="1">
-        <v>1126</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <v>576</v>
-      </c>
-      <c r="C43">
-        <v>512</v>
-      </c>
-      <c r="D43">
-        <v>495</v>
+        <v>38</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1126</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1143</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1230</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <v>204</v>
-      </c>
-      <c r="C44">
-        <v>194</v>
-      </c>
-      <c r="D44">
-        <v>134</v>
+        <v>16</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1069</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1096</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1172</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B45" s="1">
-        <v>156915</v>
+        <v>1057</v>
       </c>
       <c r="C45" s="1">
-        <v>154328</v>
+        <v>1075</v>
       </c>
       <c r="D45" s="1">
-        <v>153567</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2715</v>
+        <v>24</v>
+      </c>
+      <c r="B46">
+        <v>995</v>
       </c>
       <c r="C46" s="1">
-        <v>2674</v>
+        <v>1030</v>
       </c>
       <c r="D46" s="1">
-        <v>2575</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B47">
-        <v>905</v>
-      </c>
-      <c r="C47">
-        <v>858</v>
-      </c>
-      <c r="D47">
-        <v>832</v>
+        <v>958</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1019</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B48">
-        <v>628</v>
+        <v>838</v>
       </c>
       <c r="C48">
-        <v>626</v>
+        <v>828</v>
       </c>
       <c r="D48">
-        <v>559</v>
+        <v>909</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1">
-        <v>10205</v>
-      </c>
-      <c r="C49" s="1">
-        <v>9899</v>
-      </c>
-      <c r="D49" s="1">
-        <v>9514</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>832</v>
+      </c>
+      <c r="C49">
+        <v>858</v>
+      </c>
+      <c r="D49">
+        <v>905</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="1">
-        <v>3460</v>
-      </c>
-      <c r="C50" s="1">
-        <v>3254</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3105</v>
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <v>804</v>
+      </c>
+      <c r="C50">
+        <v>825</v>
+      </c>
+      <c r="D50">
+        <v>902</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B51">
-        <v>189</v>
+        <v>791</v>
       </c>
       <c r="C51">
-        <v>177</v>
+        <v>789</v>
       </c>
       <c r="D51">
-        <v>161</v>
+        <v>869</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1294</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1190</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1232</v>
+        <v>29</v>
+      </c>
+      <c r="B52">
+        <v>740</v>
+      </c>
+      <c r="C52">
+        <v>780</v>
+      </c>
+      <c r="D52">
+        <v>776</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1019</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1020</v>
+        <v>27</v>
+      </c>
+      <c r="B53">
+        <v>650</v>
+      </c>
+      <c r="C53">
+        <v>698</v>
       </c>
       <c r="D53">
-        <v>958</v>
+        <v>751</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2969</v>
-      </c>
-      <c r="C54" s="1">
-        <v>2745</v>
-      </c>
-      <c r="D54" s="1">
-        <v>2656</v>
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <v>561</v>
+      </c>
+      <c r="C54">
+        <v>552</v>
+      </c>
+      <c r="D54">
+        <v>644</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B55">
-        <v>264</v>
+        <v>559</v>
       </c>
       <c r="C55">
-        <v>248</v>
+        <v>626</v>
       </c>
       <c r="D55">
-        <v>216</v>
+        <v>628</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56" s="1">
-        <v>29716</v>
-      </c>
-      <c r="C56" s="1">
-        <v>28766</v>
-      </c>
-      <c r="D56" s="1">
-        <v>28182</v>
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>539</v>
+      </c>
+      <c r="C56">
+        <v>547</v>
+      </c>
+      <c r="D56">
+        <v>596</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B57">
-        <v>596</v>
+        <v>513</v>
       </c>
       <c r="C57">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D57">
-        <v>539</v>
+        <v>575</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1">
-        <v>16461</v>
-      </c>
-      <c r="C58" s="1">
-        <v>16148</v>
-      </c>
-      <c r="D58" s="1">
-        <v>15826</v>
+        <v>39</v>
+      </c>
+      <c r="B58">
+        <v>495</v>
+      </c>
+      <c r="C58">
+        <v>512</v>
+      </c>
+      <c r="D58">
+        <v>576</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B59">
-        <v>310</v>
+        <v>457</v>
       </c>
       <c r="C59">
-        <v>285</v>
+        <v>443</v>
       </c>
       <c r="D59">
-        <v>264</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2920</v>
-      </c>
-      <c r="C60" s="1">
-        <v>2835</v>
-      </c>
-      <c r="D60" s="1">
-        <v>2699</v>
+        <v>25</v>
+      </c>
+      <c r="B60">
+        <v>450</v>
+      </c>
+      <c r="C60">
+        <v>502</v>
+      </c>
+      <c r="D60">
+        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="1">
-        <v>4472</v>
-      </c>
-      <c r="C61" s="1">
-        <v>4130</v>
-      </c>
-      <c r="D61" s="1">
-        <v>4096</v>
+        <v>63</v>
+      </c>
+      <c r="B61">
+        <v>443</v>
+      </c>
+      <c r="C61">
+        <v>480</v>
+      </c>
+      <c r="D61">
+        <v>531</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B62">
+        <v>443</v>
+      </c>
+      <c r="C62">
         <v>479</v>
       </c>
-      <c r="C62">
-        <v>430</v>
-      </c>
       <c r="D62">
-        <v>389</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1337</v>
-      </c>
-      <c r="C63" s="1">
-        <v>1259</v>
-      </c>
-      <c r="D63" s="1">
-        <v>1186</v>
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>403</v>
+      </c>
+      <c r="C63">
+        <v>435</v>
+      </c>
+      <c r="D63">
+        <v>473</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1">
-        <v>9170</v>
-      </c>
-      <c r="C64" s="1">
-        <v>8859</v>
-      </c>
-      <c r="D64" s="1">
-        <v>8737</v>
+        <v>58</v>
+      </c>
+      <c r="B64">
+        <v>389</v>
+      </c>
+      <c r="C64">
+        <v>430</v>
+      </c>
+      <c r="D64">
+        <v>479</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <v>644</v>
+        <v>318</v>
       </c>
       <c r="C65">
-        <v>552</v>
+        <v>335</v>
       </c>
       <c r="D65">
-        <v>561</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3981</v>
-      </c>
-      <c r="C66" s="1">
-        <v>3996</v>
-      </c>
-      <c r="D66" s="1">
-        <v>3994</v>
+        <v>6</v>
+      </c>
+      <c r="B66">
+        <v>276</v>
+      </c>
+      <c r="C66">
+        <v>284</v>
+      </c>
+      <c r="D66">
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="B67">
-        <v>531</v>
+        <v>272</v>
       </c>
       <c r="C67">
-        <v>480</v>
+        <v>292</v>
       </c>
       <c r="D67">
-        <v>443</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B68">
-        <v>509</v>
+        <v>264</v>
       </c>
       <c r="C68">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="D68">
-        <v>443</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="1">
-        <v>12809</v>
-      </c>
-      <c r="C69" s="1">
-        <v>12469</v>
-      </c>
-      <c r="D69" s="1">
-        <v>12385</v>
+        <v>11</v>
+      </c>
+      <c r="B69">
+        <v>252</v>
+      </c>
+      <c r="C69">
+        <v>289</v>
+      </c>
+      <c r="D69">
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -2635,100 +2635,103 @@
         <v>66</v>
       </c>
       <c r="B70">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="C70">
         <v>280</v>
       </c>
       <c r="D70">
-        <v>251</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1">
-        <v>5247</v>
-      </c>
-      <c r="C71" s="1">
-        <v>5027</v>
-      </c>
-      <c r="D71" s="1">
-        <v>4826</v>
+        <v>51</v>
+      </c>
+      <c r="B71">
+        <v>216</v>
+      </c>
+      <c r="C71">
+        <v>248</v>
+      </c>
+      <c r="D71">
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1">
-        <v>23569</v>
-      </c>
-      <c r="C72" s="1">
-        <v>22536</v>
-      </c>
-      <c r="D72" s="1">
-        <v>21971</v>
+        <v>47</v>
+      </c>
+      <c r="B72">
+        <v>161</v>
+      </c>
+      <c r="C72">
+        <v>177</v>
+      </c>
+      <c r="D72">
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>69</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2039</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1917</v>
-      </c>
-      <c r="D73" s="1">
-        <v>1865</v>
+        <v>21</v>
+      </c>
+      <c r="B73">
+        <v>143</v>
+      </c>
+      <c r="C73">
+        <v>170</v>
+      </c>
+      <c r="D73">
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74" s="1">
-        <v>1786</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1719</v>
-      </c>
-      <c r="D74" s="1">
-        <v>1688</v>
+        <v>40</v>
+      </c>
+      <c r="B74">
+        <v>134</v>
+      </c>
+      <c r="C74">
+        <v>194</v>
+      </c>
+      <c r="D74">
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>71</v>
-      </c>
-      <c r="B75" s="1">
-        <v>8774</v>
-      </c>
-      <c r="C75" s="1">
-        <v>8587</v>
-      </c>
-      <c r="D75" s="1">
-        <v>8411</v>
+        <v>18</v>
+      </c>
+      <c r="B75">
+        <v>80</v>
+      </c>
+      <c r="C75">
+        <v>86</v>
+      </c>
+      <c r="D75">
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>72</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2760</v>
-      </c>
-      <c r="C76" s="1">
-        <v>2581</v>
-      </c>
-      <c r="D76" s="1">
-        <v>2430</v>
+        <v>26</v>
+      </c>
+      <c r="B76">
+        <v>63</v>
+      </c>
+      <c r="C76">
+        <v>70</v>
+      </c>
+      <c r="D76">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:D76">
+    <sortCondition descending="1" ref="B5:B76"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>